--- a/diseases/d238/2026-2029.xlsx
+++ b/diseases/d238/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>3</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.02803464128485004</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.01868976085656669</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.009344880428283346</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -3140,9 +3122,6 @@
       </c>
       <c r="O14" t="n">
         <v>1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0.009344880428283346</v>
